--- a/Pricing Logic/modules/uploads/module_4_704.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_704.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,22 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>عصير كل يوم تفاح 225 مل</t>
-  </si>
-  <si>
-    <t>كوكا كولا - 2.45 لتر</t>
-  </si>
-  <si>
-    <t>رويال أعشاب ينسون- 20 فتلة</t>
-  </si>
-  <si>
-    <t>تونة دولفين قطعة واحدة حار - 200 جم</t>
-  </si>
-  <si>
-    <t>شويبس جولد اناناس جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>بيج كولا - 360 مل</t>
+    <t>سفن اب كانز جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>اندومي  خضار حار - 48 كيس- 5 جنيه 56 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -413,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -441,7 +429,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>997</v>
+        <v>435</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -450,129 +438,27 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>123.75</v>
+        <v>301.75</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>2778</v>
+        <v>24260</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>3981</v>
-      </c>
-      <c r="B4" t="s">
         <v>9</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1296</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>3981</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>5020</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>23</v>
-      </c>
-      <c r="D6">
-        <v>59</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>5020</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>2832</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>5493</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>292</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>10992</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>104</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_704.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_704.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,19 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>سفن اب كانز جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>اندومي  خضار حار - 48 كيس- 5 جنيه 56 جم</t>
+    <t>تونة دولفين قطعة واحدة بارد - 200 جم</t>
+  </si>
+  <si>
+    <t>فانتا برتقال - 0.95 لتر</t>
+  </si>
+  <si>
+    <t>اوكسى جل يدوى ابيض و الوان نسيم الشرق - 30 جم</t>
+  </si>
+  <si>
+    <t>سندة أرز رفيع- 1 كجم</t>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,36 +438,121 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>435</v>
+        <v>947</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D2">
-        <v>301.75</v>
+        <v>1416</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24260</v>
+        <v>947</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>15</v>
+      </c>
+      <c r="D3">
+        <v>708</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>947</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>2832</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>947</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>59</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>3673</v>
+      </c>
+      <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C3">
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>127.5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>11161</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>212</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
+      <c r="D7">
+        <v>58</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>11894</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>230.25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_704.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_704.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="14">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,22 +37,25 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>تونة دولفين قطعة واحدة بارد - 200 جم</t>
-  </si>
-  <si>
-    <t>فانتا برتقال - 0.95 لتر</t>
-  </si>
-  <si>
-    <t>اوكسى جل يدوى ابيض و الوان نسيم الشرق - 30 جم</t>
-  </si>
-  <si>
-    <t>سندة أرز رفيع- 1 كجم</t>
+    <t>مكرونة حواء خواتم - 400 جم</t>
+  </si>
+  <si>
+    <t>ميرندا برتقال تربو - 390 مل</t>
+  </si>
+  <si>
+    <t>تونة دولفين مفتتة بارد - 140 جم</t>
+  </si>
+  <si>
+    <t>تونة دولفين مفتتة حار - 140 جم</t>
+  </si>
+  <si>
+    <t>بيبسي هضبه - 250 مل</t>
+  </si>
+  <si>
+    <t>YES</t>
   </si>
   <si>
     <t>NO</t>
-  </si>
-  <si>
-    <t>YES</t>
   </si>
 </sst>
 </file>
@@ -410,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -438,33 +441,33 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>947</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1416</v>
+        <v>263</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>947</v>
+        <v>1126</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>708</v>
+        <v>129.5</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -472,33 +475,33 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>947</v>
+        <v>1413</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>2832</v>
+        <v>1152</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>947</v>
+        <v>1413</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>11</v>
       </c>
       <c r="D5">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -506,16 +509,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>3673</v>
+        <v>1413</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>127.5</v>
+        <v>288</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
@@ -523,16 +526,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>11161</v>
+        <v>1413</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D7">
-        <v>58</v>
+        <v>576</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -540,18 +543,86 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>11894</v>
+        <v>1414</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
       <c r="C8">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>288</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>1414</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1152</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>1414</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>1414</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>16</v>
+      </c>
+      <c r="D11">
+        <v>576</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>25958</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12">
         <v>2</v>
       </c>
-      <c r="D8">
-        <v>230.25</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D12">
+        <v>119.25</v>
+      </c>
+      <c r="E12" t="s">
         <v>12</v>
       </c>
     </row>

--- a/Pricing Logic/modules/uploads/module_4_704.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_704.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,25 +37,13 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>مكرونة حواء خواتم - 400 جم</t>
-  </si>
-  <si>
-    <t>ميرندا برتقال تربو - 390 مل</t>
-  </si>
-  <si>
-    <t>تونة دولفين مفتتة بارد - 140 جم</t>
-  </si>
-  <si>
-    <t>تونة دولفين مفتتة حار - 140 جم</t>
-  </si>
-  <si>
-    <t>بيبسي هضبه - 250 مل</t>
+    <t>كوكا كولا جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>كورن فلاور دريم نشا - 240 جم</t>
   </si>
   <si>
     <t>YES</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -413,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -441,189 +429,53 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>36</v>
+        <v>615</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>263</v>
+        <v>291</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>1126</v>
+        <v>3134</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>129.5</v>
+        <v>19.75</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>1413</v>
+        <v>3134</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1152</v>
+        <v>948</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>1413</v>
-      </c>
-      <c r="B5" t="s">
         <v>9</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>1413</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>288</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>1413</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>16</v>
-      </c>
-      <c r="D7">
-        <v>576</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>1414</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>15</v>
-      </c>
-      <c r="D8">
-        <v>288</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>1414</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1152</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>1414</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10">
-        <v>11</v>
-      </c>
-      <c r="D10">
-        <v>24</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>1414</v>
-      </c>
-      <c r="B11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11">
-        <v>16</v>
-      </c>
-      <c r="D11">
-        <v>576</v>
-      </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>25958</v>
-      </c>
-      <c r="B12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <v>119.25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_704.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_704.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="15">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,25 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>كوكا كولا جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>كورن فلاور دريم نشا - 240 جم</t>
+    <t>جبنة عبور لاند فيتا بيضاء - 250 جم</t>
+  </si>
+  <si>
+    <t>بيبسى - 2.43 لتر</t>
+  </si>
+  <si>
+    <t>مسحوق غسيل فل ازرق يدوى - 2.5 كجم</t>
+  </si>
+  <si>
+    <t>لبان تشكلتس نعناع - 0.5 جنية</t>
+  </si>
+  <si>
+    <t>بن عبد المعبود سادة فاتح سوفت - 50 جم</t>
+  </si>
+  <si>
+    <t>شاى العروسة -.. 250 جم</t>
+  </si>
+  <si>
+    <t>بليزو وايت ويفر رول محـشو بكريمه الفانيليا مغطى بالكراميل والكرسب والشكوكلاته البيضاء - 5 جنية</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,7 +444,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>615</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -438,44 +453,180 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>291</v>
+        <v>540</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>3134</v>
+        <v>589</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>19.75</v>
+        <v>220</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>3134</v>
+        <v>3934</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>51.5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>5208</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="D4">
-        <v>948</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
+      <c r="D5">
+        <v>1552.5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>5208</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>51.75</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>6630</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>285.75</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>6630</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>3429</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>7886</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>204.25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>7886</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>2451</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24711</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>832.5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24711</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>46.25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_704.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_704.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="13">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,25 +37,19 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>جبنة عبور لاند فيتا بيضاء - 250 جم</t>
+    <t>ميرندا برتقال كانز - 320 مل</t>
+  </si>
+  <si>
+    <t>سفن اب كانز جيب - 240 مل</t>
   </si>
   <si>
     <t>بيبسى - 2.43 لتر</t>
   </si>
   <si>
-    <t>مسحوق غسيل فل ازرق يدوى - 2.5 كجم</t>
-  </si>
-  <si>
-    <t>لبان تشكلتس نعناع - 0.5 جنية</t>
-  </si>
-  <si>
-    <t>بن عبد المعبود سادة فاتح سوفت - 50 جم</t>
-  </si>
-  <si>
-    <t>شاى العروسة -.. 250 جم</t>
-  </si>
-  <si>
-    <t>بليزو وايت ويفر رول محـشو بكريمه الفانيليا مغطى بالكراميل والكرسب والشكوكلاته البيضاء - 5 جنية</t>
+    <t>ماكينة حلاقة جيليت بلو تو بلاس حصيرة - 48 ماكينة</t>
+  </si>
+  <si>
+    <t>سوفى ليلية ماكسى بالمسك طويل جدا جدا 36 سم عرض خاص - 12 فوطة</t>
   </si>
   <si>
     <t>YES</t>
@@ -416,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -444,7 +438,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -453,15 +447,15 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>540</v>
+        <v>330</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>589</v>
+        <v>435</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -470,163 +464,112 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>220</v>
+        <v>301.75</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>3934</v>
+        <v>589</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>51.5</v>
+        <v>225</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>5208</v>
+        <v>3016</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>1552.5</v>
+        <v>1170.5</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>5208</v>
+        <v>3016</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="D6">
-        <v>51.75</v>
+        <v>585.25</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>6630</v>
+        <v>3016</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>285.75</v>
+        <v>7023</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>6630</v>
+        <v>11150</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>3429</v>
+        <v>83.5</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>7886</v>
+        <v>11150</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>204.25</v>
+        <v>668</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>7886</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>2451</v>
-      </c>
-      <c r="E10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24711</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>832.5</v>
-      </c>
-      <c r="E11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24711</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12">
-        <v>46.25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_704.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_704.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,19 +37,13 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>ميرندا برتقال كانز - 320 مل</t>
-  </si>
-  <si>
-    <t>سفن اب كانز جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>بيبسى - 2.43 لتر</t>
-  </si>
-  <si>
-    <t>ماكينة حلاقة جيليت بلو تو بلاس حصيرة - 48 ماكينة</t>
-  </si>
-  <si>
-    <t>سوفى ليلية ماكسى بالمسك طويل جدا جدا 36 سم عرض خاص - 12 فوطة</t>
+    <t>عصير كل يوم جوافة  - 225 مل</t>
+  </si>
+  <si>
+    <t>زيت حلوة خليط - 4.5 لتر</t>
+  </si>
+  <si>
+    <t>مناديل زينة تريو تواليت عرض 5 + 1 رول هدية 6 بكرة</t>
   </si>
   <si>
     <t>YES</t>
@@ -410,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -438,7 +432,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>126</v>
+        <v>995</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -447,129 +441,44 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>330</v>
+        <v>123.75</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>435</v>
+        <v>4203</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>301.75</v>
+        <v>613.25</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>589</v>
+        <v>11726</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>225</v>
+        <v>289.75</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>3016</v>
-      </c>
-      <c r="B5" t="s">
         <v>10</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>1170.5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>3016</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>68</v>
-      </c>
-      <c r="D6">
-        <v>585.25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>3016</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>7023</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>11150</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>83.5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>11150</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>668</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_704.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_704.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="34">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,82 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>شويبس رمان جيب - 240 مل</t>
+    <t>فاين مناديل فلافي جيب- 10 باكت</t>
+  </si>
+  <si>
+    <t>مسحوق كيك دريم مكس برتقال - 400 جم</t>
+  </si>
+  <si>
+    <t>كلوريل كلور 2*1 ليمون اصفر - 1 كجم</t>
+  </si>
+  <si>
+    <t>بريكس منظف ارضيات صنوبر - 3 لتر</t>
+  </si>
+  <si>
+    <t>شاى الكبوس ناعم - 30 جم</t>
+  </si>
+  <si>
+    <t>فاين بيبى حفاضات دبل لوك صغير مقاس 2 - 58 حفاضة</t>
+  </si>
+  <si>
+    <t>فاين بيبى حفاضات دبل لوك وسط مقاس 3 - 58 حفاضة</t>
+  </si>
+  <si>
+    <t>فاين بيبى حفاضات دبل لوك كبير مقاس 4 - 58 حفاضة</t>
+  </si>
+  <si>
+    <t>فاين بيبى حفاضات دبل لوك ماكس مقاس 5 - 58 حفاضة</t>
+  </si>
+  <si>
+    <t>أولويز ماكسى سميكة ناعمة حساس بلمسة الألوڤيرا طويلة  +2 فوطة مجانا 16 فوطة</t>
+  </si>
+  <si>
+    <t>سبيرو سباتيس تفاح احمر - 330 مل</t>
+  </si>
+  <si>
+    <t>سبيرو سباتيس يوسفي - 330 مل</t>
+  </si>
+  <si>
+    <t>كوكا كولا كانز ستار - 320 مل</t>
+  </si>
+  <si>
+    <t>حفاضات بيبى جوى مضغوطة جيب مانع للتسريب صغير مقاس 2 - 60 حفاضة</t>
+  </si>
+  <si>
+    <t>اوكسى سائل اطباق ليمون أصفر ظرف 35 جرام</t>
+  </si>
+  <si>
+    <t>ويفر لمبادا مينى 5 اكس - 5 جنية</t>
+  </si>
+  <si>
+    <t>حفاضات فاين بيبى مقاس 3 دبل لوك - 80 حفاضة</t>
+  </si>
+  <si>
+    <t>حفاضات فاين بيبى ماكسى مقاس 4 دبل لوك - 80 حفاضة</t>
+  </si>
+  <si>
+    <t>حفاضات فاين بيبى كبير مقاس 5 دبل لوك - 76 حفاضة</t>
+  </si>
+  <si>
+    <t>فاين برستيج 500 منديل * 3 طبقة 500 منديل</t>
+  </si>
+  <si>
+    <t>فاين برستيج عرض خاص 500 منديل  "6 شرينك" * 3 طبقة 500 منديل</t>
+  </si>
+  <si>
+    <t>فاين ديل مناديل وجه 380 منديل *2 طبقة عبوة التوفير 380 منديل</t>
+  </si>
+  <si>
+    <t>فاين سوبر مناديل مطبخ 2 رول * 2 طبقة 2 رول</t>
+  </si>
+  <si>
+    <t>فاين سوبر مناديل مطبخ 5+1 رول * 2 طبقة 6 رول</t>
+  </si>
+  <si>
+    <t>سبيرو سباتس كولا - 330 جم</t>
+  </si>
+  <si>
+    <t>بيبسى كانز ستار زيادة %10- 355 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,19 +501,631 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>5491</v>
+        <v>308</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>173.5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>407</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>576</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>407</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>48</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>1853</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>158</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>3453</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>407.5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>9082</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>12.25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>9082</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1837.5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>9207</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>25</v>
+      </c>
+      <c r="D9">
+        <v>247.75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>9207</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>29</v>
+      </c>
+      <c r="D10">
+        <v>743.25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>9208</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>29</v>
+      </c>
+      <c r="D11">
+        <v>886.5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>9208</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <v>25</v>
+      </c>
+      <c r="D12">
+        <v>295.5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>9209</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>898.5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>9209</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <v>25</v>
+      </c>
+      <c r="D14">
+        <v>299.5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>9239</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15">
+        <v>25</v>
+      </c>
+      <c r="D15">
+        <v>340.75</v>
+      </c>
+      <c r="E15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>9239</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>29</v>
+      </c>
+      <c r="D16">
+        <v>1022.25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>9840</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>612</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>9840</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18">
+        <v>25</v>
+      </c>
+      <c r="D18">
+        <v>38.25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>9964</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19">
         <v>2</v>
       </c>
-      <c r="D2">
-        <v>291.25</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
+      <c r="D19">
+        <v>110</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>9967</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>110</v>
+      </c>
+      <c r="E20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>11396</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>323</v>
+      </c>
+      <c r="E21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>11426</v>
+      </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22">
+        <v>25</v>
+      </c>
+      <c r="D22">
+        <v>263.75</v>
+      </c>
+      <c r="E22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>11426</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>29</v>
+      </c>
+      <c r="D23">
+        <v>791.25</v>
+      </c>
+      <c r="E23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>11587</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>68.5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>12501</v>
+      </c>
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>96</v>
+      </c>
+      <c r="E25" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>13257</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26">
+        <v>29</v>
+      </c>
+      <c r="D26">
+        <v>734</v>
+      </c>
+      <c r="E26" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>13257</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27">
+        <v>25</v>
+      </c>
+      <c r="D27">
+        <v>367</v>
+      </c>
+      <c r="E27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>13258</v>
+      </c>
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28">
+        <v>29</v>
+      </c>
+      <c r="D28">
+        <v>746</v>
+      </c>
+      <c r="E28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>13258</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29">
+        <v>25</v>
+      </c>
+      <c r="D29">
+        <v>373</v>
+      </c>
+      <c r="E29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>13259</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30">
+        <v>29</v>
+      </c>
+      <c r="D30">
+        <v>848</v>
+      </c>
+      <c r="E30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>13259</v>
+      </c>
+      <c r="B31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31">
+        <v>25</v>
+      </c>
+      <c r="D31">
+        <v>424</v>
+      </c>
+      <c r="E31" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>13263</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32">
+        <v>29</v>
+      </c>
+      <c r="D32">
+        <v>413.75</v>
+      </c>
+      <c r="E32" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>13264</v>
+      </c>
+      <c r="B33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33">
+        <v>29</v>
+      </c>
+      <c r="D33">
+        <v>411.5</v>
+      </c>
+      <c r="E33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>13266</v>
+      </c>
+      <c r="B34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34">
+        <v>29</v>
+      </c>
+      <c r="D34">
+        <v>264.25</v>
+      </c>
+      <c r="E34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>13273</v>
+      </c>
+      <c r="B35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35">
+        <v>29</v>
+      </c>
+      <c r="D35">
+        <v>241.75</v>
+      </c>
+      <c r="E35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>13274</v>
+      </c>
+      <c r="B36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36">
+        <v>29</v>
+      </c>
+      <c r="D36">
+        <v>228.5</v>
+      </c>
+      <c r="E36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>13893</v>
+      </c>
+      <c r="B37" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37">
+        <v>110</v>
+      </c>
+      <c r="E37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38">
+        <v>25899</v>
+      </c>
+      <c r="B38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38">
+        <v>338</v>
+      </c>
+      <c r="E38" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_704.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_704.xlsx
@@ -37,7 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>مسحوق باهى يدوى لافندر - 215 جم</t>
+    <t>مكرونة الملكة فرن - 400 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -426,7 +426,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>11813</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -435,7 +435,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>95.75</v>
+        <v>258.5</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>

--- a/Pricing Logic/modules/uploads/module_4_704.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_704.xlsx
@@ -37,7 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>مكرونة الملكة فرن - 400 جم</t>
+    <t>مسحوق باهى يدوى لافندر 12 كيس- 135 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -426,7 +426,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>25</v>
+        <v>24566</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -435,7 +435,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>258.5</v>
+        <v>89.5</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>

--- a/Pricing Logic/modules/uploads/module_4_704.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_704.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="30">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,70 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>مسحوق باهى يدوى لافندر 12 كيس- 135 جم</t>
+    <t>باندا مثلثات - 8 قطعه</t>
+  </si>
+  <si>
+    <t>باندا مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مثلثات - 8 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية جبنة كريمى  بالقشطة - 4 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية جبنة مربعات ب القشطة - 6 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مربعات جبنة بالقشطة - 8 قطعه</t>
+  </si>
+  <si>
+    <t>ديرى مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا بلس  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا  - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا بلس - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا 250 جرام</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا 125 جرام</t>
+  </si>
+  <si>
+    <t>عرض باندا ( 2علبة باندا250 جم + علبة فول باندا 400جم) - 900 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,7 +489,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24566</v>
+        <v>21704</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -435,10 +498,503 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>89.5</v>
+        <v>693</v>
       </c>
       <c r="E2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21704</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>19.25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21705</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>870</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21705</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>36.25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21706</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>26.75</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21706</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>963</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21707</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1272</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21707</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21708</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21708</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1040</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21709</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1132.5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21709</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13">
+        <v>37.75</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21710</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>49</v>
+      </c>
+      <c r="E14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21710</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1470</v>
+      </c>
+      <c r="E15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21713</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>630</v>
+      </c>
+      <c r="E16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>21713</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <v>26.25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>21752</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>474.25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>21754</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>417.5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>21771</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>417.5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>21773</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>368.5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21774</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>474.25</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>21777</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>368.5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>21778</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>474.25</v>
+      </c>
+      <c r="E24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>21779</v>
+      </c>
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>417.5</v>
+      </c>
+      <c r="E25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>21781</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>283</v>
+      </c>
+      <c r="E26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>21783</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>356.5</v>
+      </c>
+      <c r="E27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>21789</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>310</v>
+      </c>
+      <c r="E28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>22125</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>474.25</v>
+      </c>
+      <c r="E29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>22126</v>
+      </c>
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>368.5</v>
+      </c>
+      <c r="E30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>25775</v>
+      </c>
+      <c r="B31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <v>280</v>
+      </c>
+      <c r="E31" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_704.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_704.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,82 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>نوفى فينجرز أصابع البسكويت مغطاه بشيكولاتة الحليب - 5 جنية</t>
-  </si>
-  <si>
-    <t>نوفي فينجرز شيكولاتة بيضاء - 5 جنية</t>
+    <t>فاين مناديل فلافي جيب- 10 باكت</t>
+  </si>
+  <si>
+    <t>زيت قلية خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت حلوة خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>هنادى زيت خليط- 700 مل</t>
+  </si>
+  <si>
+    <t>هنادى زيت خليط- 2.1 لتر</t>
+  </si>
+  <si>
+    <t>زيت حلوة خليط - 2.25 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت عافية عباد الشمس - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>زيت صنى خليط عباد الشمس - 2.4 لتر</t>
+  </si>
+  <si>
+    <t>هنادى زيت خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 6 زجاجة - 1.6 لتر</t>
+  </si>
+  <si>
+    <t>زيت حلوة خليط - 4.5 لتر</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة - 3.5 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 540 مل</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس - 5 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1.8 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 6 زجاجة - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال الممتاز خليط - 2.5 لتر</t>
+  </si>
+  <si>
+    <t>زيت قلية خليط - 4.5 لتر</t>
+  </si>
+  <si>
+    <t>زيت صنى للقلى و التحمير و الطبخ - 4.4 لتر</t>
+  </si>
+  <si>
+    <t>زيت عافية عباد الشمس - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 550 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,7 +501,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21686</v>
+        <v>308</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -438,61 +510,435 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>294</v>
+        <v>180.75</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21686</v>
+        <v>470</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>24.5</v>
+        <v>863.5</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21687</v>
+        <v>856</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>288</v>
+        <v>869</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21687</v>
+        <v>857</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
+        <v>627.75</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>858</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>605</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>1091</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>655</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>1490</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>604</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>1492</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>860</v>
+      </c>
+      <c r="E9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>2537</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>802</v>
+      </c>
+      <c r="E10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>2608</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>725.25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>2851</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>861.25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>2879</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>810</v>
+      </c>
+      <c r="E13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>2935</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>892.5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>4203</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>640</v>
+      </c>
+      <c r="E15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>6497</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>855</v>
+      </c>
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>7520</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1464.75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>8926</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>495</v>
+      </c>
+      <c r="E18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>9070</v>
+      </c>
+      <c r="B19" t="s">
         <v>24</v>
       </c>
-      <c r="E5" t="s">
-        <v>9</v>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>895</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>9358</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>554</v>
+      </c>
+      <c r="E20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>11962</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>681.75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>11965</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>705.25</v>
+      </c>
+      <c r="E22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>11968</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1262</v>
+      </c>
+      <c r="E23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>12150</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1273.75</v>
+      </c>
+      <c r="E24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>12661</v>
+      </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>387</v>
+      </c>
+      <c r="E25" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>12923</v>
+      </c>
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>855</v>
+      </c>
+      <c r="E26" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>12925</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>490</v>
+      </c>
+      <c r="E27" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_704.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_704.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,82 +37,34 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>فاين مناديل فلافي جيب- 10 باكت</t>
-  </si>
-  <si>
-    <t>زيت قلية خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت حلوة خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>هنادى زيت خليط- 700 مل</t>
-  </si>
-  <si>
-    <t>هنادى زيت خليط- 2.1 لتر</t>
-  </si>
-  <si>
-    <t>زيت حلوة خليط - 2.25 لتر</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت عافية عباد الشمس - 2.2 لتر</t>
-  </si>
-  <si>
-    <t>زيت صنى خليط عباد الشمس - 2.4 لتر</t>
-  </si>
-  <si>
-    <t>هنادى زيت خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 6 زجاجة - 1.6 لتر</t>
-  </si>
-  <si>
-    <t>زيت حلوة خليط - 4.5 لتر</t>
-  </si>
-  <si>
-    <t>سندة زيت خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة - 3.5 لتر</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 540 مل</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس - 5 لتر</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 1.8 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة 6 زجاجة - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال الممتاز خليط - 2.5 لتر</t>
+    <t>سندة زيت خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 900 مل</t>
+  </si>
+  <si>
+    <t>صابون كامى حيوية - 110 جم</t>
   </si>
   <si>
     <t>زيت قلية خليط - 4.5 لتر</t>
   </si>
   <si>
-    <t>زيت صنى للقلى و التحمير و الطبخ - 4.4 لتر</t>
-  </si>
-  <si>
-    <t>زيت عافية عباد الشمس - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 550 مل</t>
+    <t>توشيبا احمر قلم كارت AA - 4 حجر</t>
+  </si>
+  <si>
+    <t>توشيبا احمر ريموت كارت AAA - 4 حجر</t>
+  </si>
+  <si>
+    <t>AA توشيبا ازرق 4 حجر قلم شرنك 4 حجر</t>
+  </si>
+  <si>
+    <t>ليندو برو برائحه اللافندر - 1.5 كجم</t>
+  </si>
+  <si>
+    <t>ليندو برو برائحه اللافندر  - 2 كجم</t>
+  </si>
+  <si>
+    <t>جبنة دومتي بلس بالزيتون - 500 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -473,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -501,7 +453,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>308</v>
+        <v>6494</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -510,15 +462,15 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>180.75</v>
+        <v>615</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>470</v>
+        <v>6496</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -527,418 +479,231 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>863.5</v>
+        <v>772</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>856</v>
+        <v>8284</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>869</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>857</v>
+        <v>8284</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>627.75</v>
+        <v>696</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>858</v>
+        <v>11968</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>605</v>
+        <v>1262</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>1091</v>
+        <v>12607</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>655</v>
+        <v>370</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>1490</v>
+        <v>12607</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>604</v>
+        <v>1850</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>1492</v>
+        <v>12608</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>860</v>
+        <v>370</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>2537</v>
+        <v>12608</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>802</v>
+        <v>1850</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>2608</v>
+        <v>12677</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>725.25</v>
+        <v>275</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>2851</v>
+        <v>12677</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D12">
-        <v>861.25</v>
+        <v>1375</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>2879</v>
+        <v>12677</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>810</v>
+        <v>6875</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>2935</v>
+        <v>13604</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14">
-        <v>892.5</v>
+        <v>284.25</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>4203</v>
+        <v>13606</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>640</v>
+        <v>366</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>6497</v>
+        <v>19983</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>855</v>
+        <v>460</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>7520</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>1464.75</v>
-      </c>
-      <c r="E17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>8926</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>495</v>
-      </c>
-      <c r="E18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>9070</v>
-      </c>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>895</v>
-      </c>
-      <c r="E19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>9358</v>
-      </c>
-      <c r="B20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>554</v>
-      </c>
-      <c r="E20" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>11962</v>
-      </c>
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>681.75</v>
-      </c>
-      <c r="E21" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>11965</v>
-      </c>
-      <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>705.25</v>
-      </c>
-      <c r="E22" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>11968</v>
-      </c>
-      <c r="B23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>1262</v>
-      </c>
-      <c r="E23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>12150</v>
-      </c>
-      <c r="B24" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>1273.75</v>
-      </c>
-      <c r="E24" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>12661</v>
-      </c>
-      <c r="B25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>387</v>
-      </c>
-      <c r="E25" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>12923</v>
-      </c>
-      <c r="B26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>855</v>
-      </c>
-      <c r="E26" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>12925</v>
-      </c>
-      <c r="B27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>490</v>
-      </c>
-      <c r="E27" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_704.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_704.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,34 +37,16 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>سندة زيت خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>سندة زيت خليط - 900 مل</t>
-  </si>
-  <si>
-    <t>صابون كامى حيوية - 110 جم</t>
-  </si>
-  <si>
-    <t>زيت قلية خليط - 4.5 لتر</t>
-  </si>
-  <si>
     <t>توشيبا احمر قلم كارت AA - 4 حجر</t>
   </si>
   <si>
     <t>توشيبا احمر ريموت كارت AAA - 4 حجر</t>
   </si>
   <si>
-    <t>AA توشيبا ازرق 4 حجر قلم شرنك 4 حجر</t>
-  </si>
-  <si>
     <t>ليندو برو برائحه اللافندر - 1.5 كجم</t>
   </si>
   <si>
     <t>ليندو برو برائحه اللافندر  - 2 كجم</t>
-  </si>
-  <si>
-    <t>جبنة دومتي بلس بالزيتون - 500 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -425,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -453,257 +435,104 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>6494</v>
+        <v>12607</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>615</v>
+        <v>370</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>6496</v>
+        <v>12607</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>772</v>
+        <v>1850</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>8284</v>
+        <v>12608</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>58</v>
+        <v>370</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>8284</v>
+        <v>12608</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>696</v>
+        <v>1850</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>11968</v>
+        <v>13604</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>1262</v>
+        <v>284.25</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>12607</v>
+        <v>13606</v>
       </c>
       <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>366</v>
+      </c>
+      <c r="E7" t="s">
         <v>11</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>370</v>
-      </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>12607</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1850</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>12608</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>370</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>12608</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1850</v>
-      </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>12677</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <v>275</v>
-      </c>
-      <c r="E11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>12677</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12">
-        <v>1375</v>
-      </c>
-      <c r="E12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>12677</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>6875</v>
-      </c>
-      <c r="E13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>13604</v>
-      </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>284.25</v>
-      </c>
-      <c r="E14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>13606</v>
-      </c>
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>366</v>
-      </c>
-      <c r="E15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19983</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>460</v>
-      </c>
-      <c r="E16" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_704.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_704.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,16 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>توشيبا احمر قلم كارت AA - 4 حجر</t>
-  </si>
-  <si>
-    <t>توشيبا احمر ريموت كارت AAA - 4 حجر</t>
-  </si>
-  <si>
-    <t>ليندو برو برائحه اللافندر - 1.5 كجم</t>
-  </si>
-  <si>
-    <t>ليندو برو برائحه اللافندر  - 2 كجم</t>
+    <t>سمن كريستال ابيض صفيحة - 4.25 كجم</t>
   </si>
   <si>
     <t>YES</t>
@@ -407,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -435,104 +426,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>12607</v>
+        <v>4926</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D2">
-        <v>370</v>
+        <v>388.5</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>12607</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1850</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>12608</v>
-      </c>
-      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>370</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>12608</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1850</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>13604</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>284.25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>13606</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>366</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
